--- a/docs/TraceabilityMatrix.xlsx
+++ b/docs/TraceabilityMatrix.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -922,6 +922,33 @@
         </is>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>TC-CFG-001</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Configuration change: set a service config variable, apply and restart all; the value takes effect and all services return Online.</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>tests/test_config_change.py::test_config_change_and_restart</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
